--- a/data/game_data.xlsx
+++ b/data/game_data.xlsx
@@ -9,18 +9,20 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20316" windowHeight="3840"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20316" windowHeight="3840" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="character_stat" sheetId="1" r:id="rId1"/>
     <sheet name="monster_stat" sheetId="2" r:id="rId2"/>
+    <sheet name="event" sheetId="4" r:id="rId3"/>
+    <sheet name="battle_event" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="109">
   <si>
     <t>name</t>
   </si>
@@ -43,21 +45,9 @@
     <t>type</t>
   </si>
   <si>
-    <t>아이리 칸나</t>
-  </si>
-  <si>
     <t>1기생</t>
   </si>
   <si>
-    <t>신화,용,무희</t>
-  </si>
-  <si>
-    <t>노래로 적을 제압</t>
-  </si>
-  <si>
-    <t>#3B82F6</t>
-  </si>
-  <si>
     <t>outdoor</t>
   </si>
   <si>
@@ -193,40 +183,223 @@
     <t>허수아비</t>
   </si>
   <si>
-    <t>몸풀기</t>
-  </si>
-  <si>
     <t>군단</t>
   </si>
   <si>
     <t>악플</t>
   </si>
   <si>
-    <t>딜측정</t>
-  </si>
-  <si>
     <t>경찰</t>
   </si>
   <si>
-    <t>고득점용</t>
-  </si>
-  <si>
     <t>아침</t>
   </si>
   <si>
-    <t>달력</t>
-  </si>
-  <si>
-    <t>전력</t>
-  </si>
-  <si>
     <t>보스</t>
   </si>
   <si>
-    <t>불</t>
-  </si>
-  <si>
-    <t>최고 기록</t>
+    <t>name</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>평범한 하루</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>평화롭습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>none</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>간식 배달</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>사장님의 간식</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비 고장</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비 이슈 발생! 치…지직…</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>atk_down</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>atk_up</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>팬미팅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>응원 버프!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>event</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>mult</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>화려한 고음을 질러</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>음파가 폭발하듯이 퍼져나가며 데미지를 줍니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>실수로 마이크를 떨어뜨렸지만,</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오히려 적이 당황했습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>팬들의 응원을 받아</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>초인적인 힘을 발휘했습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>평소 연습한 콤보를</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>완벽하게 성공시켰습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀여운 표정을 지어</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>적을 방심하게 만들었습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>넘어질 뻔 했지만,</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>자연스럽게 회전 회오리 킥을 날렸습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>갑자기 텐션이 올라서</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>미친듯이 딜을 넣습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>준비한 게임이 잘 작동되지 않자</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>뿌에엥하고 울기 시작했습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>급방종과 함께 마이크가 켜지고</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>자기야 나 방종했어…어?!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>팬들이 뜷어져라 쳐다보기 시작하자</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>에휴 하고 한숨을 내쉽니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>일찍 방종을 하려고 하자</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>몰려오는 천원펀치로 방종버튼 디펜스가 시작되었습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>바이러스</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>몸풀기를 위한 테스트용 몬스터입니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>방송장비에 문제가 생겼습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>딜 측정을 위해 등장했습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오니 가면</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오니</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>일본까지 가볼까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>고득점을 노리려면 때로는 위험을 감수해야 합니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>월요일 아침은 언제나 힘듭니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>최고 기록을 노려보세요!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아침</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>트로피</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1144,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
@@ -1172,25 +1345,25 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2">
-        <v>95</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
@@ -1198,7 +1371,7 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -1210,10 +1383,10 @@
         <v>15</v>
       </c>
       <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
         <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
@@ -1221,36 +1394,36 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>85</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4">
-        <v>50</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
         <v>24</v>
@@ -1259,7 +1432,7 @@
         <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
@@ -1267,13 +1440,13 @@
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -1282,7 +1455,7 @@
         <v>29</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
@@ -1290,13 +1463,13 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
       </c>
       <c r="D7">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
         <v>32</v>
@@ -1305,7 +1478,7 @@
         <v>33</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
@@ -1313,10 +1486,10 @@
         <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>60</v>
@@ -1325,125 +1498,102 @@
         <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D10">
         <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
         <v>43</v>
-      </c>
-      <c r="B11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
       </c>
       <c r="D11">
         <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
         <v>46</v>
-      </c>
-      <c r="B12" t="s">
-        <v>39</v>
       </c>
       <c r="C12" t="s">
         <v>47</v>
       </c>
       <c r="D12">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13">
-        <v>99</v>
-      </c>
-      <c r="E13" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1454,7 +1604,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
@@ -1462,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
@@ -1473,72 +1623,309 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="B2">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B4">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="B5">
-        <v>1200</v>
+        <v>550</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6">
+        <v>700</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7">
+        <v>1200</v>
+      </c>
+      <c r="C7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8">
+        <v>1500</v>
+      </c>
+      <c r="C8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
         <v>66</v>
       </c>
-      <c r="B6">
-        <v>1500</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B4" t="s">
         <v>67</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C4" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/game_data.xlsx
+++ b/data/game_data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20316" windowHeight="3840" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20316" windowHeight="3840"/>
   </bookViews>
   <sheets>
     <sheet name="character_stat" sheetId="1" r:id="rId1"/>
@@ -57,9 +57,6 @@
     <t>전설,동물,무희</t>
   </si>
   <si>
-    <t>어그로 담당</t>
-  </si>
-  <si>
     <t>#F472B6</t>
   </si>
   <si>
@@ -69,9 +66,6 @@
     <t>전설,용,탱커</t>
   </si>
   <si>
-    <t>다시태어난마룡</t>
-  </si>
-  <si>
     <t>indoor</t>
   </si>
   <si>
@@ -84,9 +78,6 @@
     <t>현대,인간,가희</t>
   </si>
   <si>
-    <t>SIUUUUU</t>
-  </si>
-  <si>
     <t>#A855F7</t>
   </si>
   <si>
@@ -96,9 +87,6 @@
     <t>우주,동물,가희</t>
   </si>
   <si>
-    <t>밍</t>
-  </si>
-  <si>
     <t>#FCD34D</t>
   </si>
   <si>
@@ -108,9 +96,6 @@
     <t>전설,뱀파이어,무희</t>
   </si>
   <si>
-    <t>강력한 파괴력</t>
-  </si>
-  <si>
     <t>#EF4444</t>
   </si>
   <si>
@@ -120,9 +105,6 @@
     <t>이세계,인간,탱커</t>
   </si>
   <si>
-    <t>기적의 용사</t>
-  </si>
-  <si>
     <t>#06B6D4</t>
   </si>
   <si>
@@ -132,33 +114,21 @@
     <t>3기생</t>
   </si>
   <si>
-    <t>여우신</t>
-  </si>
-  <si>
     <t>하나코 나나</t>
   </si>
   <si>
-    <t>다시 태어난 요원</t>
-  </si>
-  <si>
     <t>유즈하 리코</t>
   </si>
   <si>
     <t>이세계,인간,가희</t>
   </si>
   <si>
-    <t>하이용사</t>
-  </si>
-  <si>
     <t>아오쿠모 린</t>
   </si>
   <si>
     <t>현대,인간,탱커</t>
   </si>
   <si>
-    <t>뇨</t>
-  </si>
-  <si>
     <t>강지</t>
   </si>
   <si>
@@ -168,9 +138,6 @@
     <t>보스,가희</t>
   </si>
   <si>
-    <t>별의 주인</t>
-  </si>
-  <si>
     <t>#111827</t>
   </si>
   <si>
@@ -399,6 +366,50 @@
   </si>
   <si>
     <t>트로피</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>차원을 넘나들며 보물을 수집(?)하다 지구까지 넘어온 보물탐험가</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오랜 잠에서 깨어 별의 인도에 따라 다시 태어난 마룡</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>신사에 틀어박혀 게임하던 여우신</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>신분을 속이고 다시 태어난 비밀요원</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>마왕을 물리친 소원으로 지구로 오게 된 용사</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>주인님을 모시는 방법을 배우는 메이드 컨셉 아이돌</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>흡혈보다 음악을 더 좋아하게 된 혼혈 뱀파이어</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>동료를 찾기 위해 유명해지고 싶은 우주 고양이</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>바래왔던 꿈을 이루기 위해 아이돌 프로덕션에 합류하게 된 18세 여고생</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>별을 쫓아 유니콘나라에서 지구까지 온 혼혈 유니콘</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭇별들의 길을 함께하는 별의 길잡이</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1319,6 +1330,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="5" max="5" width="23.3984375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
@@ -1354,13 +1368,13 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F2" t="s">
         <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -1368,45 +1382,45 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>77</v>
+      </c>
+      <c r="E3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
         <v>14</v>
-      </c>
-      <c r="D3">
-        <v>50</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4">
+        <v>70</v>
+      </c>
+      <c r="E4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4">
-        <v>85</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
       </c>
       <c r="G4" t="s">
         <v>8</v>
@@ -1414,68 +1428,68 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D6">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G7" t="s">
         <v>8</v>
@@ -1483,22 +1497,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
       </c>
       <c r="D8">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G8" t="s">
         <v>8</v>
@@ -1506,22 +1520,22 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D9">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>101</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G9" t="s">
         <v>8</v>
@@ -1529,22 +1543,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D10">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
         <v>8</v>
@@ -1552,22 +1566,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D11">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G11" t="s">
         <v>8</v>
@@ -1575,22 +1589,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D12">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G12" t="s">
         <v>8</v>
@@ -1599,6 +1613,7 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1612,10 +1627,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
@@ -1623,100 +1638,100 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B2">
         <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B3">
         <v>300</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B4">
         <v>500</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B5">
         <v>550</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B6">
         <v>700</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B7">
         <v>1200</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B8">
         <v>1500</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1732,57 +1747,57 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1798,21 +1813,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C2">
         <v>1.5</v>
@@ -1820,10 +1835,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1831,10 +1846,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -1842,10 +1857,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C5">
         <v>2.2000000000000002</v>
@@ -1853,10 +1868,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C6">
         <v>1.1000000000000001</v>
@@ -1864,10 +1879,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C7">
         <v>1.4</v>
@@ -1875,10 +1890,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C8">
         <v>1.2</v>
@@ -1886,10 +1901,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C9">
         <v>0.5</v>
@@ -1897,10 +1912,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C10">
         <v>0.3</v>
@@ -1908,10 +1923,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1919,10 +1934,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C12">
         <v>0.8</v>

--- a/data/game_data.xlsx
+++ b/data/game_data.xlsx
@@ -1331,6 +1331,7 @@
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
+    <col min="3" max="3" width="21.8984375" customWidth="1"/>
     <col min="5" max="5" width="23.3984375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1711,7 +1712,7 @@
         <v>45</v>
       </c>
       <c r="B7">
-        <v>1200</v>
+        <v>850</v>
       </c>
       <c r="C7" t="s">
         <v>96</v>
@@ -1725,7 +1726,7 @@
         <v>46</v>
       </c>
       <c r="B8">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="C8" t="s">
         <v>97</v>

--- a/data/game_data.xlsx
+++ b/data/game_data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20316" windowHeight="3840"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20316" windowHeight="3840" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="character_stat" sheetId="1" r:id="rId1"/>
@@ -159,209 +159,206 @@
     <t>경찰</t>
   </si>
   <si>
+    <t>보스</t>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>평범한 하루</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>평화롭습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>none</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>간식 배달</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>사장님의 간식</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비 고장</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비 이슈 발생! 치…지직…</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>atk_down</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>atk_up</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>팬미팅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>응원 버프!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>event</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>mult</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>화려한 고음을 질러</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>음파가 폭발하듯이 퍼져나가며 데미지를 줍니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>실수로 마이크를 떨어뜨렸지만,</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오히려 적이 당황했습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>팬들의 응원을 받아</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>초인적인 힘을 발휘했습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>평소 연습한 콤보를</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>완벽하게 성공시켰습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀여운 표정을 지어</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>적을 방심하게 만들었습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>넘어질 뻔 했지만,</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>자연스럽게 회전 회오리 킥을 날렸습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>갑자기 텐션이 올라서</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>미친듯이 딜을 넣습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>준비한 게임이 잘 작동되지 않자</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>뿌에엥하고 울기 시작했습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>급방종과 함께 마이크가 켜지고</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>자기야 나 방종했어…어?!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>팬들이 뜷어져라 쳐다보기 시작하자</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>에휴 하고 한숨을 내쉽니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>일찍 방종을 하려고 하자</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>몰려오는 천원펀치로 방종버튼 디펜스가 시작되었습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>바이러스</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>몸풀기를 위한 테스트용 몬스터입니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>방송장비에 문제가 생겼습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>딜 측정을 위해 등장했습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오니 가면</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오니</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>일본까지 가볼까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>고득점을 노리려면 때로는 위험을 감수해야 합니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>월요일 아침은 언제나 힘듭니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>최고 기록을 노려보세요!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>아침</t>
-  </si>
-  <si>
-    <t>보스</t>
-  </si>
-  <si>
-    <t>name</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>desc</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>effect</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>평범한 하루</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>평화롭습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>none</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>간식 배달</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>사장님의 간식</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>장비 고장</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>장비 이슈 발생! 치…지직…</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>atk_down</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>atk_up</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>팬미팅</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>응원 버프!</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>event</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>mult</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>화려한 고음을 질러</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>음파가 폭발하듯이 퍼져나가며 데미지를 줍니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>실수로 마이크를 떨어뜨렸지만,</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>오히려 적이 당황했습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>팬들의 응원을 받아</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>초인적인 힘을 발휘했습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>평소 연습한 콤보를</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>완벽하게 성공시켰습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>귀여운 표정을 지어</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>적을 방심하게 만들었습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>넘어질 뻔 했지만,</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>자연스럽게 회전 회오리 킥을 날렸습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>갑자기 텐션이 올라서</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>미친듯이 딜을 넣습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>준비한 게임이 잘 작동되지 않자</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>뿌에엥하고 울기 시작했습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>급방종과 함께 마이크가 켜지고</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>자기야 나 방종했어…어?!</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>팬들이 뜷어져라 쳐다보기 시작하자</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>에휴 하고 한숨을 내쉽니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>일찍 방종을 하려고 하자</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>몰려오는 천원펀치로 방종버튼 디펜스가 시작되었습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>바이러스</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>몸풀기를 위한 테스트용 몬스터입니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>방송장비에 문제가 생겼습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>딜 측정을 위해 등장했습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>오니 가면</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>오니</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>일본까지 가볼까요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>고득점을 노리려면 때로는 위험을 감수해야 합니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>월요일 아침은 언제나 힘듭니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>최고 기록을 노려보세요!</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>아침</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -410,6 +407,10 @@
   </si>
   <si>
     <t>뭇별들의 길을 함께하는 별의 길잡이</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>월요일 아침</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1372,7 +1373,7 @@
         <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -1395,7 +1396,7 @@
         <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -1418,7 +1419,7 @@
         <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -1441,7 +1442,7 @@
         <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -1464,7 +1465,7 @@
         <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -1487,7 +1488,7 @@
         <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F7" t="s">
         <v>27</v>
@@ -1510,7 +1511,7 @@
         <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F8" t="s">
         <v>27</v>
@@ -1533,7 +1534,7 @@
         <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
         <v>27</v>
@@ -1556,7 +1557,7 @@
         <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F10" t="s">
         <v>27</v>
@@ -1579,7 +1580,7 @@
         <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F11" t="s">
         <v>27</v>
@@ -1602,7 +1603,7 @@
         <v>85</v>
       </c>
       <c r="E12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F12" t="s">
         <v>38</v>
@@ -1639,16 +1640,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B2">
         <v>150</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1662,7 +1663,7 @@
         <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1676,26 +1677,26 @@
         <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B5">
         <v>550</v>
       </c>
       <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
         <v>90</v>
-      </c>
-      <c r="D5" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B6">
         <v>700</v>
@@ -1704,35 +1705,35 @@
         <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="B7">
         <v>850</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8">
         <v>1200</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1748,57 +1749,57 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
         <v>47</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>48</v>
-      </c>
-      <c r="C1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
         <v>50</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>51</v>
-      </c>
-      <c r="C2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
         <v>53</v>
       </c>
-      <c r="B3" t="s">
-        <v>54</v>
-      </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" t="s">
         <v>59</v>
       </c>
-      <c r="B5" t="s">
-        <v>60</v>
-      </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1814,21 +1815,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" t="s">
         <v>61</v>
-      </c>
-      <c r="B1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s">
         <v>63</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
       </c>
       <c r="C2">
         <v>1.5</v>
@@ -1836,10 +1837,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
         <v>65</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -1847,10 +1848,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" t="s">
         <v>67</v>
-      </c>
-      <c r="B4" t="s">
-        <v>68</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -1858,10 +1859,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
         <v>69</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
       </c>
       <c r="C5">
         <v>2.2000000000000002</v>
@@ -1869,10 +1870,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
         <v>71</v>
-      </c>
-      <c r="B6" t="s">
-        <v>72</v>
       </c>
       <c r="C6">
         <v>1.1000000000000001</v>
@@ -1880,10 +1881,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" t="s">
         <v>73</v>
-      </c>
-      <c r="B7" t="s">
-        <v>74</v>
       </c>
       <c r="C7">
         <v>1.4</v>
@@ -1891,10 +1892,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" t="s">
         <v>75</v>
-      </c>
-      <c r="B8" t="s">
-        <v>76</v>
       </c>
       <c r="C8">
         <v>1.2</v>
@@ -1902,10 +1903,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
         <v>77</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
       </c>
       <c r="C9">
         <v>0.5</v>
@@ -1913,10 +1914,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
         <v>79</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
       </c>
       <c r="C10">
         <v>0.3</v>
@@ -1924,10 +1925,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
         <v>81</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1935,10 +1936,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" t="s">
         <v>83</v>
-      </c>
-      <c r="B12" t="s">
-        <v>84</v>
       </c>
       <c r="C12">
         <v>0.8</v>
